--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -3463,10 +3463,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117566319</v>
+        <v>117562707</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>79589</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3475,50 +3475,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493908</v>
+        <v>493948</v>
       </c>
       <c r="R26" t="n">
-        <v>6937348</v>
+        <v>6937495</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3548,18 +3536,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3578,10 +3575,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117562707</v>
+        <v>117566319</v>
       </c>
       <c r="B27" t="n">
-        <v>79589</v>
+        <v>97836</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,38 +3587,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493948</v>
+        <v>493908</v>
       </c>
       <c r="R27" t="n">
-        <v>6937495</v>
+        <v>6937348</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3651,27 +3660,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -7096,10 +7096,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117684420</v>
+        <v>117683052</v>
       </c>
       <c r="B58" t="n">
-        <v>97836</v>
+        <v>78125</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7108,25 +7108,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7136,13 +7136,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494056</v>
+        <v>493946</v>
       </c>
       <c r="R58" t="n">
-        <v>6937196</v>
+        <v>6937132</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7196,19 +7196,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117683707</v>
+        <v>117684420</v>
       </c>
       <c r="B59" t="n">
         <v>97836</v>
@@ -7241,29 +7241,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493976</v>
+        <v>494056</v>
       </c>
       <c r="R59" t="n">
-        <v>6937213</v>
+        <v>6937196</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7292,7 +7283,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7302,7 +7293,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7317,22 +7308,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117683052</v>
+        <v>117683707</v>
       </c>
       <c r="B60" t="n">
-        <v>78125</v>
+        <v>97836</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7341,38 +7332,47 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493946</v>
+        <v>493976</v>
       </c>
       <c r="R60" t="n">
-        <v>6937132</v>
+        <v>6937213</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD60" t="b">

--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117452612</v>
+        <v>117452990</v>
       </c>
       <c r="B2" t="n">
-        <v>97836</v>
+        <v>56499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494063</v>
+        <v>494055</v>
       </c>
       <c r="R2" t="n">
-        <v>6936804</v>
+        <v>6936845</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117452145</v>
+        <v>117456323</v>
       </c>
       <c r="B3" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,41 +804,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494066</v>
+        <v>494024</v>
       </c>
       <c r="R3" t="n">
-        <v>6936870</v>
+        <v>6937036</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,54 +877,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117452169</v>
+        <v>117453084</v>
       </c>
       <c r="B4" t="n">
-        <v>79561</v>
+        <v>90464</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,25 +919,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494067</v>
+        <v>494033</v>
       </c>
       <c r="R4" t="n">
-        <v>6936872</v>
+        <v>6936713</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1007,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117452436</v>
+        <v>117452672</v>
       </c>
       <c r="B5" t="n">
         <v>97836</v>
@@ -1060,7 +1054,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1074,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494055</v>
+        <v>494010</v>
       </c>
       <c r="R5" t="n">
-        <v>6936845</v>
+        <v>6936811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1128,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117453005</v>
+        <v>117452704</v>
       </c>
       <c r="B6" t="n">
-        <v>78514</v>
+        <v>90464</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,25 +1152,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1186,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494053</v>
+        <v>494010</v>
       </c>
       <c r="R6" t="n">
-        <v>6936805</v>
+        <v>6936811</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1215,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1225,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,19 +1240,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117452532</v>
+        <v>117456419</v>
       </c>
       <c r="B7" t="n">
         <v>97836</v>
@@ -1291,20 +1285,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494070</v>
+        <v>494043</v>
       </c>
       <c r="R7" t="n">
-        <v>6936846</v>
+        <v>6937046</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1331,46 +1337,37 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:51</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117456419</v>
+        <v>117452532</v>
       </c>
       <c r="B8" t="n">
         <v>97836</v>
@@ -1403,32 +1400,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494043</v>
+        <v>494070</v>
       </c>
       <c r="R8" t="n">
-        <v>6937046</v>
+        <v>6936846</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1455,40 +1440,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117452958</v>
+        <v>117452145</v>
       </c>
       <c r="B9" t="n">
-        <v>78514</v>
+        <v>57287</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,46 +1495,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>493987</v>
+        <v>494066</v>
       </c>
       <c r="R9" t="n">
-        <v>6936785</v>
+        <v>6936870</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1569,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1564,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,22 +1584,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117451875</v>
+        <v>117451838</v>
       </c>
       <c r="B10" t="n">
-        <v>79562</v>
+        <v>97836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1618,41 +1608,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494080</v>
+        <v>494130</v>
       </c>
       <c r="R10" t="n">
-        <v>6936889</v>
+        <v>6936923</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1681,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,19 +1705,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117456379</v>
+        <v>117456353</v>
       </c>
       <c r="B11" t="n">
         <v>97836</v>
@@ -1753,7 +1752,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1770,10 +1769,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494043</v>
+        <v>494071</v>
       </c>
       <c r="R11" t="n">
-        <v>6937041</v>
+        <v>6937045</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1833,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117451838</v>
+        <v>117452958</v>
       </c>
       <c r="B12" t="n">
-        <v>97836</v>
+        <v>78514</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,35 +1844,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1882,13 +1881,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494130</v>
+        <v>493987</v>
       </c>
       <c r="R12" t="n">
-        <v>6936923</v>
+        <v>6936785</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1917,7 +1916,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,7 +1926,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117452195</v>
+        <v>117451875</v>
       </c>
       <c r="B13" t="n">
-        <v>78480</v>
+        <v>79562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1994,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494082</v>
+        <v>494080</v>
       </c>
       <c r="R13" t="n">
-        <v>6936849</v>
+        <v>6936889</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,7 +2028,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,7 +2038,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2065,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117452672</v>
+        <v>117451867</v>
       </c>
       <c r="B14" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,50 +2077,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494010</v>
+        <v>494080</v>
       </c>
       <c r="R14" t="n">
-        <v>6936811</v>
+        <v>6936892</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2150,7 +2140,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,7 +2150,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2175,22 +2170,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117453012</v>
+        <v>117452250</v>
       </c>
       <c r="B15" t="n">
-        <v>78514</v>
+        <v>97836</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,25 +2194,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2227,13 +2222,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494003</v>
+        <v>494065</v>
       </c>
       <c r="R15" t="n">
-        <v>6936725</v>
+        <v>6936851</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2262,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,7 +2267,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tre plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,12 +2287,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117452625</v>
+        <v>117453085</v>
       </c>
       <c r="B17" t="n">
         <v>97836</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>493989</v>
+        <v>494055</v>
       </c>
       <c r="R17" t="n">
-        <v>6936816</v>
+        <v>6936845</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,22 +2529,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117453084</v>
+        <v>117452625</v>
       </c>
       <c r="B18" t="n">
-        <v>90464</v>
+        <v>97836</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,38 +2553,47 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>494033</v>
+        <v>493989</v>
       </c>
       <c r="R18" t="n">
-        <v>6936713</v>
+        <v>6936816</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2616,7 +2625,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2626,7 +2635,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,10 +2662,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117452704</v>
+        <v>117452195</v>
       </c>
       <c r="B19" t="n">
-        <v>90464</v>
+        <v>78480</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2665,25 +2674,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2693,10 +2702,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494010</v>
+        <v>494082</v>
       </c>
       <c r="R19" t="n">
-        <v>6936811</v>
+        <v>6936849</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2728,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2738,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2753,22 +2762,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117451867</v>
+        <v>117453005</v>
       </c>
       <c r="B20" t="n">
-        <v>79561</v>
+        <v>78514</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2781,21 +2790,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2805,13 +2814,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494080</v>
+        <v>494053</v>
       </c>
       <c r="R20" t="n">
-        <v>6936892</v>
+        <v>6936805</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2840,7 +2849,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2850,12 +2859,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117456353</v>
+        <v>117452169</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
+        <v>79561</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,50 +2898,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494071</v>
+        <v>494067</v>
       </c>
       <c r="R21" t="n">
-        <v>6937045</v>
+        <v>6936872</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,37 +2959,46 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117456323</v>
+        <v>117456379</v>
       </c>
       <c r="B22" t="n">
         <v>97836</v>
@@ -3032,7 +3033,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3049,10 +3050,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494024</v>
+        <v>494043</v>
       </c>
       <c r="R22" t="n">
-        <v>6937036</v>
+        <v>6937041</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3112,10 +3113,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117452990</v>
+        <v>117452022</v>
       </c>
       <c r="B23" t="n">
-        <v>56499</v>
+        <v>57287</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3124,31 +3125,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3157,13 +3158,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494055</v>
+        <v>494060</v>
       </c>
       <c r="R23" t="n">
-        <v>6936845</v>
+        <v>6936899</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3192,7 +3193,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3202,7 +3203,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3217,22 +3218,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117452250</v>
+        <v>117453012</v>
       </c>
       <c r="B24" t="n">
-        <v>97836</v>
+        <v>78514</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3241,25 +3242,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3269,13 +3270,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494065</v>
+        <v>494003</v>
       </c>
       <c r="R24" t="n">
-        <v>6936851</v>
+        <v>6936725</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3304,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3314,12 +3315,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Tre plantor</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3334,22 +3330,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117452022</v>
+        <v>117452612</v>
       </c>
       <c r="B25" t="n">
-        <v>57287</v>
+        <v>97836</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,31 +3354,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3391,13 +3391,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>494060</v>
+        <v>494063</v>
       </c>
       <c r="R25" t="n">
-        <v>6936899</v>
+        <v>6936804</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3451,22 +3451,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117562707</v>
+        <v>117566327</v>
       </c>
       <c r="B26" t="n">
-        <v>79589</v>
+        <v>97836</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3475,38 +3475,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493948</v>
+        <v>493915</v>
       </c>
       <c r="R26" t="n">
-        <v>6937495</v>
+        <v>6937354</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3536,27 +3548,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3575,7 +3578,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117566319</v>
+        <v>117561386</v>
       </c>
       <c r="B27" t="n">
         <v>97836</v>
@@ -3610,7 +3613,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3618,19 +3621,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>493908</v>
+        <v>494044</v>
       </c>
       <c r="R27" t="n">
-        <v>6937348</v>
+        <v>6937146</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3660,18 +3660,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3690,7 +3699,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117566193</v>
+        <v>117566178</v>
       </c>
       <c r="B28" t="n">
         <v>97836</v>
@@ -3725,7 +3734,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3742,10 +3751,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493924</v>
+        <v>493919</v>
       </c>
       <c r="R28" t="n">
-        <v>6937427</v>
+        <v>6937439</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3805,7 +3814,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117561404</v>
+        <v>117566285</v>
       </c>
       <c r="B29" t="n">
         <v>97836</v>
@@ -3840,7 +3849,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3848,16 +3857,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>494044</v>
+        <v>493904</v>
       </c>
       <c r="R29" t="n">
-        <v>6937146</v>
+        <v>6937271</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3887,27 +3899,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3926,10 +3929,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117566068</v>
+        <v>117566049</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3938,41 +3941,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gärdsjögucken , Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494002</v>
+        <v>494017</v>
       </c>
       <c r="R30" t="n">
-        <v>6937125</v>
+        <v>6937083</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4032,7 +4044,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117566049</v>
+        <v>117566062</v>
       </c>
       <c r="B31" t="n">
         <v>97836</v>
@@ -4067,7 +4079,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4084,10 +4096,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494017</v>
+        <v>494002</v>
       </c>
       <c r="R31" t="n">
-        <v>6937083</v>
+        <v>6937122</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4147,10 +4159,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117566205</v>
+        <v>117566312</v>
       </c>
       <c r="B32" t="n">
-        <v>57440</v>
+        <v>97836</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4159,35 +4171,39 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4195,10 +4211,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493909</v>
+        <v>493889</v>
       </c>
       <c r="R32" t="n">
-        <v>6937412</v>
+        <v>6937288</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4239,6 +4255,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4257,10 +4274,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117562427</v>
+        <v>117566223</v>
       </c>
       <c r="B33" t="n">
-        <v>78217</v>
+        <v>97836</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4269,38 +4286,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>494022</v>
+        <v>493918</v>
       </c>
       <c r="R33" t="n">
-        <v>6937429</v>
+        <v>6937397</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4330,27 +4359,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4369,10 +4389,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117561304</v>
+        <v>117566409</v>
       </c>
       <c r="B34" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4381,47 +4401,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>494020</v>
+        <v>493887</v>
       </c>
       <c r="R34" t="n">
-        <v>6937190</v>
+        <v>6937299</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4451,27 +4465,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4490,7 +4495,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117562846</v>
+        <v>117566193</v>
       </c>
       <c r="B35" t="n">
         <v>97836</v>
@@ -4525,7 +4530,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4533,16 +4538,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493946</v>
+        <v>493924</v>
       </c>
       <c r="R35" t="n">
-        <v>6937503</v>
+        <v>6937427</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4572,27 +4580,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4611,10 +4610,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117566082</v>
+        <v>117561841</v>
       </c>
       <c r="B36" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4623,50 +4622,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>493904</v>
+        <v>494094</v>
       </c>
       <c r="R36" t="n">
-        <v>6937443</v>
+        <v>6937302</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4696,18 +4683,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4726,10 +4722,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117566285</v>
+        <v>117562673</v>
       </c>
       <c r="B37" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4738,50 +4734,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493904</v>
+        <v>493975</v>
       </c>
       <c r="R37" t="n">
-        <v>6937271</v>
+        <v>6937483</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4811,18 +4795,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4841,10 +4834,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117566053</v>
+        <v>117566068</v>
       </c>
       <c r="B38" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4857,21 +4850,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4880,14 +4873,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken , Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494000</v>
+        <v>494002</v>
       </c>
       <c r="R38" t="n">
-        <v>6937102</v>
+        <v>6937125</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4947,10 +4940,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117566077</v>
+        <v>117562632</v>
       </c>
       <c r="B39" t="n">
-        <v>97836</v>
+        <v>79098</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4959,50 +4952,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493915</v>
+        <v>493977</v>
       </c>
       <c r="R39" t="n">
-        <v>6937471</v>
+        <v>6937481</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5032,18 +5013,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5062,7 +5052,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117566312</v>
+        <v>117561304</v>
       </c>
       <c r="B40" t="n">
         <v>97836</v>
@@ -5097,7 +5087,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5105,19 +5095,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>493889</v>
+        <v>494020</v>
       </c>
       <c r="R40" t="n">
-        <v>6937288</v>
+        <v>6937190</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5147,18 +5134,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5177,7 +5173,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117566223</v>
+        <v>117566319</v>
       </c>
       <c r="B41" t="n">
         <v>97836</v>
@@ -5212,7 +5208,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5229,10 +5225,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>493918</v>
+        <v>493908</v>
       </c>
       <c r="R41" t="n">
-        <v>6937397</v>
+        <v>6937348</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5292,10 +5288,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117566500</v>
+        <v>117566234</v>
       </c>
       <c r="B42" t="n">
-        <v>79561</v>
+        <v>97836</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5304,30 +5300,39 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5335,10 +5340,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493900</v>
+        <v>493928</v>
       </c>
       <c r="R42" t="n">
-        <v>6937352</v>
+        <v>6937396</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5398,10 +5403,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117562632</v>
+        <v>117566257</v>
       </c>
       <c r="B43" t="n">
-        <v>79098</v>
+        <v>97836</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5410,38 +5415,50 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493977</v>
+        <v>493912</v>
       </c>
       <c r="R43" t="n">
-        <v>6937481</v>
+        <v>6937265</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5471,27 +5488,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5510,10 +5518,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117561841</v>
+        <v>117566345</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5522,38 +5530,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>494094</v>
+        <v>493894</v>
       </c>
       <c r="R44" t="n">
-        <v>6937302</v>
+        <v>6937318</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5583,27 +5603,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5622,7 +5633,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117566062</v>
+        <v>117566082</v>
       </c>
       <c r="B45" t="n">
         <v>97836</v>
@@ -5657,7 +5668,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5674,10 +5685,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>494002</v>
+        <v>493904</v>
       </c>
       <c r="R45" t="n">
-        <v>6937122</v>
+        <v>6937443</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5737,7 +5748,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117566335</v>
+        <v>117566246</v>
       </c>
       <c r="B46" t="n">
         <v>97836</v>
@@ -5789,10 +5800,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493900</v>
+        <v>493916</v>
       </c>
       <c r="R46" t="n">
-        <v>6937338</v>
+        <v>6937337</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5852,7 +5863,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117566297</v>
+        <v>117566212</v>
       </c>
       <c r="B47" t="n">
         <v>97836</v>
@@ -5887,7 +5898,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -5904,10 +5915,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493895</v>
+        <v>493904</v>
       </c>
       <c r="R47" t="n">
-        <v>6937275</v>
+        <v>6937385</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5967,10 +5978,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117566327</v>
+        <v>117562707</v>
       </c>
       <c r="B48" t="n">
-        <v>97836</v>
+        <v>79589</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5979,50 +5990,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493915</v>
+        <v>493948</v>
       </c>
       <c r="R48" t="n">
-        <v>6937354</v>
+        <v>6937495</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6052,18 +6051,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6082,10 +6090,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117566257</v>
+        <v>117566205</v>
       </c>
       <c r="B49" t="n">
-        <v>97836</v>
+        <v>57440</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6094,39 +6102,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6134,10 +6138,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493912</v>
+        <v>493909</v>
       </c>
       <c r="R49" t="n">
-        <v>6937265</v>
+        <v>6937412</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6178,7 +6182,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6197,7 +6200,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117566345</v>
+        <v>117566077</v>
       </c>
       <c r="B50" t="n">
         <v>97836</v>
@@ -6232,7 +6235,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6249,10 +6252,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493894</v>
+        <v>493915</v>
       </c>
       <c r="R50" t="n">
-        <v>6937318</v>
+        <v>6937471</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6312,7 +6315,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117566246</v>
+        <v>117562846</v>
       </c>
       <c r="B51" t="n">
         <v>97836</v>
@@ -6347,7 +6350,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6355,19 +6358,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493916</v>
+        <v>493946</v>
       </c>
       <c r="R51" t="n">
-        <v>6937337</v>
+        <v>6937503</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6397,18 +6397,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6427,10 +6436,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117566212</v>
+        <v>117566359</v>
       </c>
       <c r="B52" t="n">
-        <v>97836</v>
+        <v>90499</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6439,39 +6448,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493904</v>
+        <v>493925</v>
       </c>
       <c r="R52" t="n">
-        <v>6937385</v>
+        <v>6937389</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6542,10 +6542,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117566234</v>
+        <v>117562427</v>
       </c>
       <c r="B53" t="n">
-        <v>97836</v>
+        <v>78217</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6554,50 +6554,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493928</v>
+        <v>494022</v>
       </c>
       <c r="R53" t="n">
-        <v>6937396</v>
+        <v>6937429</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6627,18 +6615,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6657,10 +6654,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117566359</v>
+        <v>117566335</v>
       </c>
       <c r="B54" t="n">
-        <v>90499</v>
+        <v>97836</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6669,30 +6666,39 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6700,10 +6706,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493925</v>
+        <v>493900</v>
       </c>
       <c r="R54" t="n">
-        <v>6937389</v>
+        <v>6937338</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6763,10 +6769,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117562673</v>
+        <v>117566053</v>
       </c>
       <c r="B55" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6779,34 +6785,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493975</v>
+        <v>494000</v>
       </c>
       <c r="R55" t="n">
-        <v>6937483</v>
+        <v>6937102</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6836,27 +6845,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117566409</v>
+        <v>117566500</v>
       </c>
       <c r="B56" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6891,21 +6891,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493887</v>
+        <v>493900</v>
       </c>
       <c r="R56" t="n">
-        <v>6937299</v>
+        <v>6937352</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6981,7 +6981,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117566178</v>
+        <v>117566297</v>
       </c>
       <c r="B57" t="n">
         <v>97836</v>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493919</v>
+        <v>493895</v>
       </c>
       <c r="R57" t="n">
-        <v>6937439</v>
+        <v>6937275</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7096,10 +7096,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117683052</v>
+        <v>117684343</v>
       </c>
       <c r="B58" t="n">
-        <v>78125</v>
+        <v>97836</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7108,38 +7108,47 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493946</v>
+        <v>494042</v>
       </c>
       <c r="R58" t="n">
-        <v>6937132</v>
+        <v>6937189</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7171,7 +7180,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7181,7 +7190,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7208,10 +7217,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117684420</v>
+        <v>117683052</v>
       </c>
       <c r="B59" t="n">
-        <v>97836</v>
+        <v>78125</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7220,25 +7229,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7248,13 +7257,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>494056</v>
+        <v>493946</v>
       </c>
       <c r="R59" t="n">
-        <v>6937196</v>
+        <v>6937132</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7283,7 +7292,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7293,7 +7302,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7308,22 +7317,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117683707</v>
+        <v>117683300</v>
       </c>
       <c r="B60" t="n">
-        <v>97836</v>
+        <v>78480</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7332,47 +7341,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493976</v>
+        <v>493904</v>
       </c>
       <c r="R60" t="n">
-        <v>6937213</v>
+        <v>6937176</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7441,7 +7441,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117684343</v>
+        <v>117683150</v>
       </c>
       <c r="B61" t="n">
         <v>97836</v>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>494042</v>
+        <v>493922</v>
       </c>
       <c r="R61" t="n">
-        <v>6937189</v>
+        <v>6937130</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>117683718</v>
+        <v>117682920</v>
       </c>
       <c r="B62" t="n">
         <v>78480</v>
@@ -7602,10 +7602,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493978</v>
+        <v>493973</v>
       </c>
       <c r="R62" t="n">
-        <v>6937214</v>
+        <v>6937081</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7637,7 +7637,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7647,7 +7647,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7674,10 +7674,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117682920</v>
+        <v>117682862</v>
       </c>
       <c r="B63" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7686,38 +7686,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493973</v>
+        <v>493998</v>
       </c>
       <c r="R63" t="n">
-        <v>6937081</v>
+        <v>6937074</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7749,7 +7758,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7759,7 +7768,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7786,10 +7795,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117685349</v>
+        <v>117684546</v>
       </c>
       <c r="B64" t="n">
-        <v>79098</v>
+        <v>79562</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7802,21 +7811,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7826,10 +7835,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494029</v>
+        <v>494058</v>
       </c>
       <c r="R64" t="n">
-        <v>6937398</v>
+        <v>6937201</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7861,7 +7870,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7871,7 +7880,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7898,10 +7907,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117685602</v>
+        <v>117683718</v>
       </c>
       <c r="B65" t="n">
-        <v>90464</v>
+        <v>78480</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7910,25 +7919,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7938,10 +7947,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>494008</v>
+        <v>493978</v>
       </c>
       <c r="R65" t="n">
-        <v>6937428</v>
+        <v>6937214</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7973,7 +7982,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7983,7 +7992,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8010,10 +8019,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117682862</v>
+        <v>117685349</v>
       </c>
       <c r="B66" t="n">
-        <v>97836</v>
+        <v>79098</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8022,47 +8031,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493998</v>
+        <v>494029</v>
       </c>
       <c r="R66" t="n">
-        <v>6937074</v>
+        <v>6937398</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8131,7 +8131,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117683181</v>
+        <v>117684420</v>
       </c>
       <c r="B67" t="n">
         <v>97836</v>
@@ -8164,29 +8164,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>493924</v>
+        <v>494056</v>
       </c>
       <c r="R67" t="n">
-        <v>6937149</v>
+        <v>6937196</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8215,7 +8206,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8225,7 +8216,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8240,22 +8231,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117685481</v>
+        <v>117683181</v>
       </c>
       <c r="B68" t="n">
-        <v>79098</v>
+        <v>97836</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8264,38 +8255,47 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>494010</v>
+        <v>493924</v>
       </c>
       <c r="R68" t="n">
-        <v>6937418</v>
+        <v>6937149</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8364,7 +8364,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117683150</v>
+        <v>117682898</v>
       </c>
       <c r="B69" t="n">
         <v>97836</v>
@@ -8413,10 +8413,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493922</v>
+        <v>493973</v>
       </c>
       <c r="R69" t="n">
-        <v>6937130</v>
+        <v>6937081</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8448,7 +8448,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8485,7 +8485,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117682898</v>
+        <v>117683707</v>
       </c>
       <c r="B70" t="n">
         <v>97836</v>
@@ -8534,10 +8534,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493973</v>
+        <v>493976</v>
       </c>
       <c r="R70" t="n">
-        <v>6937081</v>
+        <v>6937213</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8606,10 +8606,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117684546</v>
+        <v>117689678</v>
       </c>
       <c r="B71" t="n">
-        <v>79562</v>
+        <v>97836</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8618,41 +8618,53 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>494058</v>
+        <v>493940</v>
       </c>
       <c r="R71" t="n">
-        <v>6937201</v>
+        <v>6937192</v>
       </c>
       <c r="S71" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8679,49 +8691,40 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117689678</v>
+        <v>117685481</v>
       </c>
       <c r="B72" t="n">
-        <v>97836</v>
+        <v>79098</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8730,53 +8733,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>493940</v>
+        <v>494010</v>
       </c>
       <c r="R72" t="n">
-        <v>6937192</v>
+        <v>6937418</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8803,40 +8794,49 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117683254</v>
+        <v>117685602</v>
       </c>
       <c r="B73" t="n">
-        <v>97836</v>
+        <v>90464</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8845,47 +8845,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493935</v>
+        <v>494008</v>
       </c>
       <c r="R73" t="n">
-        <v>6937188</v>
+        <v>6937428</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8917,7 +8908,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8927,7 +8918,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9071,10 +9062,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117683300</v>
+        <v>117683254</v>
       </c>
       <c r="B75" t="n">
-        <v>78480</v>
+        <v>97836</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9083,38 +9074,47 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493904</v>
+        <v>493935</v>
       </c>
       <c r="R75" t="n">
-        <v>6937176</v>
+        <v>6937188</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117452990</v>
+        <v>117452022</v>
       </c>
       <c r="B2" t="n">
-        <v>56499</v>
+        <v>57288</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494055</v>
+        <v>494060</v>
       </c>
       <c r="R2" t="n">
-        <v>6936845</v>
+        <v>6936899</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117456323</v>
+        <v>117451825</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,7 +827,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,19 +835,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494024</v>
+        <v>494092</v>
       </c>
       <c r="R3" t="n">
-        <v>6937036</v>
+        <v>6936893</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,18 +874,27 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117453084</v>
+        <v>117452532</v>
       </c>
       <c r="B4" t="n">
-        <v>90464</v>
+        <v>97838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494033</v>
+        <v>494070</v>
       </c>
       <c r="R4" t="n">
-        <v>6936713</v>
+        <v>6936846</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117452672</v>
+        <v>117452250</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,29 +1058,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494010</v>
+        <v>494065</v>
       </c>
       <c r="R5" t="n">
-        <v>6936811</v>
+        <v>6936851</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1110,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tre plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117452704</v>
+        <v>117451875</v>
       </c>
       <c r="B6" t="n">
-        <v>90464</v>
+        <v>79564</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,25 +1154,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,13 +1182,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494010</v>
+        <v>494080</v>
       </c>
       <c r="R6" t="n">
-        <v>6936811</v>
+        <v>6936889</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117456419</v>
+        <v>117451867</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,53 +1266,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494043</v>
+        <v>494080</v>
       </c>
       <c r="R7" t="n">
-        <v>6937046</v>
+        <v>6936892</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,40 +1327,54 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117452532</v>
+        <v>117452169</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,25 +1383,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,13 +1411,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494070</v>
+        <v>494067</v>
       </c>
       <c r="R8" t="n">
-        <v>6936846</v>
+        <v>6936872</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1442,7 +1446,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1456,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117452145</v>
+        <v>117456379</v>
       </c>
       <c r="B9" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1491,41 +1495,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494066</v>
+        <v>494043</v>
       </c>
       <c r="R9" t="n">
-        <v>6936870</v>
+        <v>6937041</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,54 +1568,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på grov tall</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117451838</v>
+        <v>117452958</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
+        <v>78516</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,35 +1610,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1645,13 +1647,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494130</v>
+        <v>493987</v>
       </c>
       <c r="R10" t="n">
-        <v>6936923</v>
+        <v>6936785</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,7 +1682,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1692,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117456353</v>
+        <v>117453012</v>
       </c>
       <c r="B11" t="n">
-        <v>97836</v>
+        <v>78516</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,50 +1731,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494071</v>
+        <v>494003</v>
       </c>
       <c r="R11" t="n">
-        <v>6937045</v>
+        <v>6936725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,18 +1792,27 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1832,10 +1831,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117452958</v>
+        <v>117452672</v>
       </c>
       <c r="B12" t="n">
-        <v>78514</v>
+        <v>97838</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1844,35 +1843,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1881,13 +1880,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>493987</v>
+        <v>494010</v>
       </c>
       <c r="R12" t="n">
-        <v>6936785</v>
+        <v>6936811</v>
       </c>
       <c r="S12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1916,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1926,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,22 +1940,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117451875</v>
+        <v>117456323</v>
       </c>
       <c r="B13" t="n">
-        <v>79562</v>
+        <v>97838</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,41 +1964,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494080</v>
+        <v>494024</v>
       </c>
       <c r="R13" t="n">
-        <v>6936889</v>
+        <v>6937036</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2026,49 +2037,40 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117451867</v>
+        <v>117452625</v>
       </c>
       <c r="B14" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,41 +2079,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494080</v>
+        <v>493989</v>
       </c>
       <c r="R14" t="n">
-        <v>6936892</v>
+        <v>6936816</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2140,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2150,12 +2161,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,22 +2176,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117452250</v>
+        <v>117453005</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
+        <v>78516</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,25 +2200,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2222,13 +2228,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494065</v>
+        <v>494053</v>
       </c>
       <c r="R15" t="n">
-        <v>6936851</v>
+        <v>6936805</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2257,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,12 +2273,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Tre plantor</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117451825</v>
+        <v>117456353</v>
       </c>
       <c r="B16" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,7 +2335,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2342,16 +2343,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>494092</v>
+        <v>494071</v>
       </c>
       <c r="R16" t="n">
-        <v>6936893</v>
+        <v>6937045</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,27 +2385,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2420,10 +2415,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117453085</v>
+        <v>117452436</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2455,7 +2450,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2504,7 +2499,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2514,7 +2509,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2541,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117452625</v>
+        <v>117456419</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2576,7 +2571,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2584,16 +2579,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>493989</v>
+        <v>494043</v>
       </c>
       <c r="R18" t="n">
-        <v>6936816</v>
+        <v>6937046</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2623,27 +2621,18 @@
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2662,10 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117452195</v>
+        <v>117452990</v>
       </c>
       <c r="B19" t="n">
-        <v>78480</v>
+        <v>56500</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,41 +2663,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>494082</v>
+        <v>494055</v>
       </c>
       <c r="R19" t="n">
-        <v>6936849</v>
+        <v>6936845</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2737,7 +2731,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2747,7 +2741,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2762,22 +2756,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117453005</v>
+        <v>117453084</v>
       </c>
       <c r="B20" t="n">
-        <v>78514</v>
+        <v>90466</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,25 +2780,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2814,10 +2808,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>494053</v>
+        <v>494033</v>
       </c>
       <c r="R20" t="n">
-        <v>6936805</v>
+        <v>6936713</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2849,7 +2843,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2859,7 +2853,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2874,22 +2868,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117452169</v>
+        <v>117452704</v>
       </c>
       <c r="B21" t="n">
-        <v>79561</v>
+        <v>90466</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2898,25 +2892,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2926,10 +2920,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>494067</v>
+        <v>494010</v>
       </c>
       <c r="R21" t="n">
-        <v>6936872</v>
+        <v>6936811</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2961,7 +2955,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2971,7 +2965,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,22 +2980,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117456379</v>
+        <v>117451838</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3033,30 +3027,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>494043</v>
+        <v>494130</v>
       </c>
       <c r="R22" t="n">
-        <v>6937041</v>
+        <v>6936923</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3083,40 +3074,49 @@
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-06-01</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117452022</v>
+        <v>117452145</v>
       </c>
       <c r="B23" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3147,24 +3147,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>494060</v>
+        <v>494066</v>
       </c>
       <c r="R23" t="n">
-        <v>6936899</v>
+        <v>6936870</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3193,7 +3188,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3203,7 +3198,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på grov tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3218,22 +3218,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117453012</v>
+        <v>117452195</v>
       </c>
       <c r="B24" t="n">
-        <v>78514</v>
+        <v>78482</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>494003</v>
+        <v>494082</v>
       </c>
       <c r="R24" t="n">
-        <v>6936725</v>
+        <v>6936849</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,12 +3330,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Anders Wännström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3345,7 +3345,7 @@
         <v>117452612</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3463,10 +3463,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117566327</v>
+        <v>117566068</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3475,50 +3475,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken , Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>493915</v>
+        <v>494002</v>
       </c>
       <c r="R26" t="n">
-        <v>6937354</v>
+        <v>6937125</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,10 +3569,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117561386</v>
+        <v>117561304</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3613,7 +3604,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3627,10 +3618,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>494044</v>
+        <v>494020</v>
       </c>
       <c r="R27" t="n">
-        <v>6937146</v>
+        <v>6937190</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3699,10 +3690,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117566178</v>
+        <v>117566409</v>
       </c>
       <c r="B28" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3711,39 +3702,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3751,10 +3733,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>493919</v>
+        <v>493887</v>
       </c>
       <c r="R28" t="n">
-        <v>6937439</v>
+        <v>6937299</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3814,10 +3796,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117566285</v>
+        <v>117562707</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
+        <v>79591</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3826,50 +3808,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>493904</v>
+        <v>493948</v>
       </c>
       <c r="R29" t="n">
-        <v>6937271</v>
+        <v>6937495</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3899,18 +3869,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3929,10 +3908,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117566049</v>
+        <v>117566312</v>
       </c>
       <c r="B30" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3964,7 +3943,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3981,10 +3960,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>494017</v>
+        <v>493889</v>
       </c>
       <c r="R30" t="n">
-        <v>6937083</v>
+        <v>6937288</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4044,10 +4023,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117566062</v>
+        <v>117566500</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
+        <v>79563</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4056,39 +4035,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4096,10 +4066,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>494002</v>
+        <v>493900</v>
       </c>
       <c r="R31" t="n">
-        <v>6937122</v>
+        <v>6937352</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4159,10 +4129,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117566312</v>
+        <v>117566049</v>
       </c>
       <c r="B32" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4194,7 +4164,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4211,10 +4181,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>493889</v>
+        <v>494017</v>
       </c>
       <c r="R32" t="n">
-        <v>6937288</v>
+        <v>6937083</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4274,10 +4244,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117566223</v>
+        <v>117566212</v>
       </c>
       <c r="B33" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4309,7 +4279,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4326,10 +4296,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>493918</v>
+        <v>493904</v>
       </c>
       <c r="R33" t="n">
-        <v>6937397</v>
+        <v>6937385</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4389,10 +4359,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117566409</v>
+        <v>117566257</v>
       </c>
       <c r="B34" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4401,30 +4371,39 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4432,10 +4411,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>493887</v>
+        <v>493912</v>
       </c>
       <c r="R34" t="n">
-        <v>6937299</v>
+        <v>6937265</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4495,10 +4474,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117566193</v>
+        <v>117566178</v>
       </c>
       <c r="B35" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4530,7 +4509,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4547,10 +4526,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>493924</v>
+        <v>493919</v>
       </c>
       <c r="R35" t="n">
-        <v>6937427</v>
+        <v>6937439</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4610,10 +4589,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117561841</v>
+        <v>117566193</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4622,38 +4601,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>494094</v>
+        <v>493924</v>
       </c>
       <c r="R36" t="n">
-        <v>6937302</v>
+        <v>6937427</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4683,27 +4674,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4722,10 +4704,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117562673</v>
+        <v>117566062</v>
       </c>
       <c r="B37" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4734,38 +4716,50 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>493975</v>
+        <v>494002</v>
       </c>
       <c r="R37" t="n">
-        <v>6937483</v>
+        <v>6937122</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4795,27 +4789,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4834,10 +4819,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117566068</v>
+        <v>117561841</v>
       </c>
       <c r="B38" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4868,19 +4853,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gärdsjögucken , Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>494002</v>
+        <v>494094</v>
       </c>
       <c r="R38" t="n">
-        <v>6937125</v>
+        <v>6937302</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4910,18 +4892,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4940,10 +4931,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117562632</v>
+        <v>117562427</v>
       </c>
       <c r="B39" t="n">
-        <v>79098</v>
+        <v>78219</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4956,21 +4947,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4980,10 +4971,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>493977</v>
+        <v>494022</v>
       </c>
       <c r="R39" t="n">
-        <v>6937481</v>
+        <v>6937429</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5052,10 +5043,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117561304</v>
+        <v>117566246</v>
       </c>
       <c r="B40" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5087,7 +5078,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5095,16 +5086,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>494020</v>
+        <v>493916</v>
       </c>
       <c r="R40" t="n">
-        <v>6937190</v>
+        <v>6937337</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5134,27 +5128,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5176,7 +5161,7 @@
         <v>117566319</v>
       </c>
       <c r="B41" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5288,10 +5273,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117566234</v>
+        <v>117566345</v>
       </c>
       <c r="B42" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5323,7 +5308,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5340,10 +5325,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>493928</v>
+        <v>493894</v>
       </c>
       <c r="R42" t="n">
-        <v>6937396</v>
+        <v>6937318</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5403,10 +5388,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117566257</v>
+        <v>117566223</v>
       </c>
       <c r="B43" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5438,7 +5423,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5455,10 +5440,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>493912</v>
+        <v>493918</v>
       </c>
       <c r="R43" t="n">
-        <v>6937265</v>
+        <v>6937397</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5518,10 +5503,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117566345</v>
+        <v>117566077</v>
       </c>
       <c r="B44" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5553,7 +5538,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5570,10 +5555,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>493894</v>
+        <v>493915</v>
       </c>
       <c r="R44" t="n">
-        <v>6937318</v>
+        <v>6937471</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5633,10 +5618,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117566082</v>
+        <v>117562846</v>
       </c>
       <c r="B45" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5668,7 +5653,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>120</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5676,19 +5661,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>493904</v>
+        <v>493946</v>
       </c>
       <c r="R45" t="n">
-        <v>6937443</v>
+        <v>6937503</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5718,18 +5700,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5748,10 +5739,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117566246</v>
+        <v>117566082</v>
       </c>
       <c r="B46" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5783,7 +5774,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5800,10 +5791,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>493916</v>
+        <v>493904</v>
       </c>
       <c r="R46" t="n">
-        <v>6937337</v>
+        <v>6937443</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5863,10 +5854,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117566212</v>
+        <v>117566359</v>
       </c>
       <c r="B47" t="n">
-        <v>97836</v>
+        <v>90501</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5875,39 +5866,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5915,10 +5897,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>493904</v>
+        <v>493925</v>
       </c>
       <c r="R47" t="n">
-        <v>6937385</v>
+        <v>6937389</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5978,10 +5960,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117562707</v>
+        <v>117566053</v>
       </c>
       <c r="B48" t="n">
-        <v>79589</v>
+        <v>78219</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5990,38 +5972,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>493948</v>
+        <v>494000</v>
       </c>
       <c r="R48" t="n">
-        <v>6937495</v>
+        <v>6937102</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6051,27 +6036,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6090,10 +6066,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117566205</v>
+        <v>117566327</v>
       </c>
       <c r="B49" t="n">
-        <v>57440</v>
+        <v>97838</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6102,35 +6078,39 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6138,10 +6118,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>493909</v>
+        <v>493915</v>
       </c>
       <c r="R49" t="n">
-        <v>6937412</v>
+        <v>6937354</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6182,6 +6162,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6200,10 +6181,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117566077</v>
+        <v>117562632</v>
       </c>
       <c r="B50" t="n">
-        <v>97836</v>
+        <v>79100</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6212,50 +6193,38 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>493915</v>
+        <v>493977</v>
       </c>
       <c r="R50" t="n">
-        <v>6937471</v>
+        <v>6937481</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6285,18 +6254,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6315,10 +6293,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117562846</v>
+        <v>117566234</v>
       </c>
       <c r="B51" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6350,7 +6328,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -6358,16 +6336,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>493946</v>
+        <v>493928</v>
       </c>
       <c r="R51" t="n">
-        <v>6937503</v>
+        <v>6937396</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6397,27 +6378,18 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6436,10 +6408,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117566359</v>
+        <v>117566285</v>
       </c>
       <c r="B52" t="n">
-        <v>90499</v>
+        <v>97838</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6448,30 +6420,39 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
@@ -6479,10 +6460,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>493925</v>
+        <v>493904</v>
       </c>
       <c r="R52" t="n">
-        <v>6937389</v>
+        <v>6937271</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6542,10 +6523,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117562427</v>
+        <v>117562673</v>
       </c>
       <c r="B53" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6558,21 +6539,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6582,10 +6563,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>494022</v>
+        <v>493975</v>
       </c>
       <c r="R53" t="n">
-        <v>6937429</v>
+        <v>6937483</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6654,10 +6635,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117566335</v>
+        <v>117566205</v>
       </c>
       <c r="B54" t="n">
-        <v>97836</v>
+        <v>57441</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6666,39 +6647,35 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6706,10 +6683,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493900</v>
+        <v>493909</v>
       </c>
       <c r="R54" t="n">
-        <v>6937338</v>
+        <v>6937412</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6750,7 +6727,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6769,10 +6745,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117566053</v>
+        <v>117561404</v>
       </c>
       <c r="B55" t="n">
-        <v>78217</v>
+        <v>97838</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6781,41 +6757,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494000</v>
+        <v>494044</v>
       </c>
       <c r="R55" t="n">
-        <v>6937102</v>
+        <v>6937146</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6845,18 +6827,27 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6875,10 +6866,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117566500</v>
+        <v>117566297</v>
       </c>
       <c r="B56" t="n">
-        <v>79561</v>
+        <v>97838</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6887,30 +6878,39 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6918,10 +6918,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493900</v>
+        <v>493895</v>
       </c>
       <c r="R56" t="n">
-        <v>6937352</v>
+        <v>6937275</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6981,10 +6981,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>117566297</v>
+        <v>117566335</v>
       </c>
       <c r="B57" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493895</v>
+        <v>493900</v>
       </c>
       <c r="R57" t="n">
-        <v>6937275</v>
+        <v>6937338</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7096,10 +7096,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117684343</v>
+        <v>117683420</v>
       </c>
       <c r="B58" t="n">
-        <v>97836</v>
+        <v>57288</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7108,35 +7108,31 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7145,10 +7141,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>494042</v>
+        <v>493904</v>
       </c>
       <c r="R58" t="n">
-        <v>6937189</v>
+        <v>6937172</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -7180,7 +7176,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7190,7 +7186,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7217,10 +7213,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117683052</v>
+        <v>117689678</v>
       </c>
       <c r="B59" t="n">
-        <v>78125</v>
+        <v>97838</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7229,41 +7225,53 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493946</v>
+        <v>493940</v>
       </c>
       <c r="R59" t="n">
-        <v>6937132</v>
+        <v>6937192</v>
       </c>
       <c r="S59" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7290,49 +7298,40 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:07</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>117683300</v>
+        <v>117683052</v>
       </c>
       <c r="B60" t="n">
-        <v>78480</v>
+        <v>78127</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7345,21 +7344,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7369,10 +7368,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493904</v>
+        <v>493946</v>
       </c>
       <c r="R60" t="n">
-        <v>6937176</v>
+        <v>6937132</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7404,7 +7403,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7414,7 +7413,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7441,10 +7440,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>117683150</v>
+        <v>117685349</v>
       </c>
       <c r="B61" t="n">
-        <v>97836</v>
+        <v>79100</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7453,47 +7452,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>493922</v>
+        <v>494029</v>
       </c>
       <c r="R61" t="n">
-        <v>6937130</v>
+        <v>6937398</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7525,7 +7515,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7535,7 +7525,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7565,7 +7555,7 @@
         <v>117682920</v>
       </c>
       <c r="B62" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7674,10 +7664,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>117682862</v>
+        <v>117683300</v>
       </c>
       <c r="B63" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7686,47 +7676,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493998</v>
+        <v>493904</v>
       </c>
       <c r="R63" t="n">
-        <v>6937074</v>
+        <v>6937176</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7758,7 +7739,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7768,7 +7749,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7795,10 +7776,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>117684546</v>
+        <v>117684420</v>
       </c>
       <c r="B64" t="n">
-        <v>79562</v>
+        <v>97838</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7807,25 +7788,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7835,13 +7816,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>494058</v>
+        <v>494056</v>
       </c>
       <c r="R64" t="n">
-        <v>6937201</v>
+        <v>6937196</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7870,7 +7851,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7880,7 +7861,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7895,22 +7876,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>117683718</v>
+        <v>117683181</v>
       </c>
       <c r="B65" t="n">
-        <v>78480</v>
+        <v>97838</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7919,38 +7900,47 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493978</v>
+        <v>493924</v>
       </c>
       <c r="R65" t="n">
-        <v>6937214</v>
+        <v>6937149</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7982,7 +7972,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7992,7 +7982,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8019,10 +8009,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117685349</v>
+        <v>117684546</v>
       </c>
       <c r="B66" t="n">
-        <v>79098</v>
+        <v>79564</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8035,21 +8025,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8059,10 +8049,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>494029</v>
+        <v>494058</v>
       </c>
       <c r="R66" t="n">
-        <v>6937398</v>
+        <v>6937201</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -8094,7 +8084,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8104,7 +8094,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8131,10 +8121,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>117684420</v>
+        <v>117683718</v>
       </c>
       <c r="B67" t="n">
-        <v>97836</v>
+        <v>78482</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8143,25 +8133,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8171,13 +8161,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>494056</v>
+        <v>493978</v>
       </c>
       <c r="R67" t="n">
-        <v>6937196</v>
+        <v>6937214</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8206,7 +8196,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8216,7 +8206,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8231,22 +8221,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>117683181</v>
+        <v>117683707</v>
       </c>
       <c r="B68" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8278,7 +8268,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8292,10 +8282,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>493924</v>
+        <v>493976</v>
       </c>
       <c r="R68" t="n">
-        <v>6937149</v>
+        <v>6937213</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -8327,7 +8317,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8337,7 +8327,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8364,10 +8354,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>117682898</v>
+        <v>117685602</v>
       </c>
       <c r="B69" t="n">
-        <v>97836</v>
+        <v>90466</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8376,47 +8366,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>493973</v>
+        <v>494008</v>
       </c>
       <c r="R69" t="n">
-        <v>6937081</v>
+        <v>6937428</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8448,7 +8429,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8458,7 +8439,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8485,10 +8466,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>117683707</v>
+        <v>117683254</v>
       </c>
       <c r="B70" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8520,7 +8501,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8534,10 +8515,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493976</v>
+        <v>493935</v>
       </c>
       <c r="R70" t="n">
-        <v>6937213</v>
+        <v>6937188</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8569,7 +8550,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8579,7 +8560,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8606,10 +8587,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>117689678</v>
+        <v>117682898</v>
       </c>
       <c r="B71" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8641,7 +8622,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8649,22 +8630,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>493940</v>
+        <v>493973</v>
       </c>
       <c r="R71" t="n">
-        <v>6937192</v>
+        <v>6937081</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8691,30 +8669,39 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8724,7 +8711,7 @@
         <v>117685481</v>
       </c>
       <c r="B72" t="n">
-        <v>79098</v>
+        <v>79100</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8833,10 +8820,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117685602</v>
+        <v>117683150</v>
       </c>
       <c r="B73" t="n">
-        <v>90464</v>
+        <v>97838</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8845,38 +8832,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>494008</v>
+        <v>493922</v>
       </c>
       <c r="R73" t="n">
-        <v>6937428</v>
+        <v>6937130</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8908,7 +8904,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8918,7 +8914,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8945,10 +8941,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>117683420</v>
+        <v>117682862</v>
       </c>
       <c r="B74" t="n">
-        <v>57287</v>
+        <v>97838</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8957,31 +8953,35 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8990,10 +8990,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>493904</v>
+        <v>493998</v>
       </c>
       <c r="R74" t="n">
-        <v>6937172</v>
+        <v>6937074</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9062,10 +9062,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>117683254</v>
+        <v>117684343</v>
       </c>
       <c r="B75" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>493935</v>
+        <v>494042</v>
       </c>
       <c r="R75" t="n">
-        <v>6937188</v>
+        <v>6937189</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9183,10 +9183,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>117720982</v>
+        <v>117720707</v>
       </c>
       <c r="B76" t="n">
-        <v>79069</v>
+        <v>56500</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9195,38 +9195,43 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gärdsjögucken  (Gärdsjögucken ), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>494114</v>
+        <v>494202</v>
       </c>
       <c r="R76" t="n">
-        <v>6937167</v>
+        <v>6937036</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9295,10 +9300,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>117720707</v>
+        <v>117720982</v>
       </c>
       <c r="B77" t="n">
-        <v>56499</v>
+        <v>79071</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9307,43 +9312,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken  (Gärdsjögucken ), Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>494202</v>
+        <v>494114</v>
       </c>
       <c r="R77" t="n">
-        <v>6937036</v>
+        <v>6937167</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>

--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -6523,10 +6523,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117562673</v>
+        <v>117561404</v>
       </c>
       <c r="B53" t="n">
-        <v>78482</v>
+        <v>97838</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6535,38 +6535,47 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gärdsjön (Gärdsjön), Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>493975</v>
+        <v>494044</v>
       </c>
       <c r="R53" t="n">
-        <v>6937483</v>
+        <v>6937146</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6635,10 +6644,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117566205</v>
+        <v>117562673</v>
       </c>
       <c r="B54" t="n">
-        <v>57441</v>
+        <v>78482</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6651,42 +6660,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjön (Gärdsjön), Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>493909</v>
+        <v>493975</v>
       </c>
       <c r="R54" t="n">
-        <v>6937412</v>
+        <v>6937483</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6716,9 +6717,19 @@
           <t>2024-06-05</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6745,10 +6756,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>117561404</v>
+        <v>117566205</v>
       </c>
       <c r="B55" t="n">
-        <v>97838</v>
+        <v>57441</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6757,47 +6768,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>494044</v>
+        <v>493909</v>
       </c>
       <c r="R55" t="n">
-        <v>6937146</v>
+        <v>6937412</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6827,19 +6837,9 @@
           <t>2024-06-05</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-06-05</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>09:38</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7096,10 +7096,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>117683420</v>
+        <v>117689678</v>
       </c>
       <c r="B58" t="n">
-        <v>57288</v>
+        <v>97838</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7108,46 +7108,53 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493904</v>
+        <v>493940</v>
       </c>
       <c r="R58" t="n">
-        <v>6937172</v>
+        <v>6937192</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7174,49 +7181,40 @@
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>117689678</v>
+        <v>117683420</v>
       </c>
       <c r="B59" t="n">
-        <v>97838</v>
+        <v>57288</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7225,53 +7223,46 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Gärdsjögucken, Jmt</t>
+          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493940</v>
+        <v>493904</v>
       </c>
       <c r="R59" t="n">
-        <v>6937192</v>
+        <v>6937172</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7298,30 +7289,39 @@
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-06-10</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8708,10 +8708,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>117685481</v>
+        <v>117683150</v>
       </c>
       <c r="B72" t="n">
-        <v>79100</v>
+        <v>97838</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8720,38 +8720,47 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494010</v>
+        <v>493922</v>
       </c>
       <c r="R72" t="n">
-        <v>6937418</v>
+        <v>6937130</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8783,7 +8792,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8793,7 +8802,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8820,10 +8829,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>117683150</v>
+        <v>117685481</v>
       </c>
       <c r="B73" t="n">
-        <v>97838</v>
+        <v>79100</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8832,47 +8841,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>493922</v>
+        <v>494010</v>
       </c>
       <c r="R73" t="n">
-        <v>6937130</v>
+        <v>6937418</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117452022</v>
       </c>
       <c r="B2" t="n">
-        <v>57288</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3116,7 +3116,7 @@
         <v>117452145</v>
       </c>
       <c r="B23" t="n">
-        <v>57288</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -8267,7 +8267,7 @@
         <v>117683420</v>
       </c>
       <c r="B68" t="n">
-        <v>57288</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gärdsjögucken (Gärdsjögucken), Jmt</t>
+          <t>Gärdsjögucken, Gärdsjögucken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">

--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117452022</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>117452145</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>117683420</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>117452022</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>117452145</v>
       </c>
       <c r="B23" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -8267,7 +8267,7 @@
         <v>117683420</v>
       </c>
       <c r="B68" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>

--- a/artfynd/A 26362-2023 artfynd.xlsx
+++ b/artfynd/A 26362-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AZ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452958</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453005</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453012</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683052</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566359</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1317,6 +1347,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451640</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451875</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684546</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1638,6 +1683,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452704</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1745,6 +1795,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453084</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1852,6 +1907,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117453136</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1959,6 +2019,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117685602</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452195</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2173,6 +2243,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561641</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561841</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2387,6 +2467,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562673</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2488,6 +2573,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566068</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2589,6 +2679,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566409</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2696,6 +2791,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117682920</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2803,6 +2903,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683300</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2910,6 +3015,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683718</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3017,6 +3127,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561878</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3124,6 +3239,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562632</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3231,6 +3351,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117685349</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3338,6 +3463,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117685481</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3450,6 +3580,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451867</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3557,6 +3692,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452169</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3658,6 +3798,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566500</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3765,6 +3910,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562707</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3877,6 +4027,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452022</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452145</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4101,6 +4261,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683420</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4213,6 +4378,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452990</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4325,6 +4495,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117720707</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4430,6 +4605,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566205</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4546,6 +4726,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451825</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4662,6 +4847,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117451838</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4774,6 +4964,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452250</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4890,6 +5085,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452436</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4997,6 +5197,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452532</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5113,6 +5318,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452612</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5229,6 +5439,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452625</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5345,6 +5560,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117452672</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5455,6 +5675,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456323</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5565,6 +5790,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456353</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5675,6 +5905,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456379</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5785,6 +6020,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456419</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5895,6 +6135,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117456450</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6011,6 +6256,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561304</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6127,6 +6377,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117561386</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6243,6 +6498,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562846</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6353,6 +6613,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566049</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6463,6 +6728,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566062</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6573,6 +6843,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566077</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6683,6 +6958,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566082</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6793,6 +7073,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566178</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6903,6 +7188,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566193</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7013,6 +7303,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566212</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7123,6 +7418,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566223</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7233,6 +7533,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566234</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7343,6 +7648,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566246</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7453,6 +7763,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566257</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7563,6 +7878,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566270</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7673,6 +7993,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566285</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7783,6 +8108,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566297</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7893,6 +8223,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566312</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8003,6 +8338,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566319</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8113,6 +8453,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566327</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8223,6 +8568,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566335</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8333,6 +8683,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566345</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8449,6 +8804,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117682862</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8565,6 +8925,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117682898</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8681,6 +9046,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683150</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8797,6 +9167,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683181</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8913,6 +9288,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683254</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9029,6 +9409,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117683707</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9145,6 +9530,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684343</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9252,6 +9642,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117684420</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9362,6 +9757,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117689678</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9472,6 +9872,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117734596</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9579,6 +9984,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117562427</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9680,6 +10090,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117566053</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9787,8 +10202,98 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117720982</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>